--- a/CodeSystem-MITRE-ATTCK-Techniques.xlsx
+++ b/CodeSystem-MITRE-ATTCK-Techniques.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.6</t>
+    <t>0.0.7</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:02:20+00:00</t>
+    <t>2026-05-14T08:13:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-MITRE-ATTCK-Techniques.xlsx
+++ b/CodeSystem-MITRE-ATTCK-Techniques.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2145" uniqueCount="1420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2143" uniqueCount="1420">
   <si>
     <t>Property</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.7</t>
+    <t>0.0.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -49,7 +49,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:13:13+00:00</t>
+    <t>2026-05-14T10:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -133,19 +133,19 @@
     <t>tactic</t>
   </si>
   <si>
-    <t>https://constir1.github.io/ATTCK2FHIR/CodeSystem/MITRE-ATTCK-Tactics</t>
-  </si>
-  <si>
-    <t>The tactic(s) this technique or subtechnique contributes to, referenced by tactic ID</t>
+    <t>The tactic(s) this technique or subtechnique contributes to (codes from the MITRE-ATTCK-Tactics CodeSystem)</t>
+  </si>
+  <si>
+    <t>Coding</t>
+  </si>
+  <si>
+    <t>parentTechnique</t>
+  </si>
+  <si>
+    <t>The parent technique of this subtechnique, referenced by ATT&amp;CK ID</t>
   </si>
   <si>
     <t>code</t>
-  </si>
-  <si>
-    <t>parentTechnique</t>
-  </si>
-  <si>
-    <t>The parent technique of this subtechnique, referenced by ATT&amp;CK ID</t>
   </si>
   <si>
     <t>isSubtechnique</t>
@@ -4596,28 +4596,24 @@
       <c r="A2" t="s" s="2">
         <v>38</v>
       </c>
-      <c r="B2" t="s" s="2">
+      <c r="B2" s="2"/>
+      <c r="C2" t="s" s="2">
         <v>39</v>
       </c>
-      <c r="C2" t="s" s="2">
+      <c r="D2" t="s" s="2">
         <v>40</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>41</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" t="s" s="2">
         <v>42</v>
       </c>
-      <c r="B3" t="s" s="2">
-        <v>3</v>
-      </c>
-      <c r="C3" t="s" s="2">
+      <c r="D3" t="s" s="2">
         <v>43</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>41</v>
       </c>
     </row>
     <row r="4">

--- a/CodeSystem-MITRE-ATTCK-Techniques.xlsx
+++ b/CodeSystem-MITRE-ATTCK-Techniques.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.8</t>
+    <t>0.0.9</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T10:01:26+00:00</t>
+    <t>2026-05-14T18:17:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-MITRE-ATTCK-Techniques.xlsx
+++ b/CodeSystem-MITRE-ATTCK-Techniques.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.9</t>
+    <t>0.0.12</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T18:17:12+00:00</t>
+    <t>2026-05-15T18:07:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-MITRE-ATTCK-Techniques.xlsx
+++ b/CodeSystem-MITRE-ATTCK-Techniques.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T18:07:37+00:00</t>
+    <t>2026-05-16T09:46:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-MITRE-ATTCK-Techniques.xlsx
+++ b/CodeSystem-MITRE-ATTCK-Techniques.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.12</t>
+    <t>0.0.13</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T09:46:24+00:00</t>
+    <t>2026-05-16T09:50:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
